--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C298"/>
+  <dimension ref="A1:C290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
         <is>
           <t>Galaxy Foldable Series
 Galaxy Z TriFold
-Galaxy Z Fold4</t>
+Galaxy Z Fold5</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold5</t>
+          <t>Galaxy Z Fold6</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold6</t>
+          <t>Galaxy Z Fold7</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold7</t>
+          <t>Galaxy Z Fold Special Edition</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold Special Edition</t>
+          <t>Galaxy Z Fold8</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold8</t>
+          <t>Galaxy Z Fold8 Ultra
+Galaxy Z Flip5</t>
         </is>
       </c>
     </row>
@@ -543,8 +544,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold8 Ultra
-Galaxy Z Flip4</t>
+          <t>Galaxy Z Flip6</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip5</t>
+          <t>Galaxy Z Flip7</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip6</t>
+          <t>Galaxy Z Flip7 FE</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7</t>
+          <t>Galaxy Z Flip8
+W23</t>
         </is>
       </c>
     </row>
@@ -604,7 +605,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7 FE</t>
+          <t>W23 Flip</t>
         </is>
       </c>
     </row>
@@ -619,8 +620,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip8
-W23</t>
+          <t>W24</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>W23 Flip</t>
+          <t>W24 Flip</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>W24 Flip</t>
+          <t>W25 Flip</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W26</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>W25 Flip</t>
+          <t>Galaxy Z TriFold</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>Galaxy Z Fold5</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Galaxy Z TriFold</t>
+          <t>Galaxy Z Fold6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold4</t>
+          <t>Galaxy Z Fold7</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold5</t>
+          <t>Galaxy Z Fold Special Edition</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold6</t>
+          <t>Galaxy Z Fold8</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold7</t>
+          <t>Galaxy Z Fold8 Ultra</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold Special Edition</t>
+          <t>Galaxy Z Flip5</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold8</t>
+          <t>Galaxy Z Flip6</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold8 Ultra</t>
+          <t>Galaxy Z Flip7</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip4</t>
+          <t>Galaxy Z Flip7 FE</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip5</t>
+          <t>Galaxy Z Flip8</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip6</t>
+          <t>W23</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7</t>
+          <t>W23 Flip</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7 FE</t>
+          <t>W24</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip8</t>
+          <t>W24 Flip</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>W23 Flip</t>
+          <t>W25 Flip</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,8 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>W24 Flip</t>
+          <t>Galaxy S Series
+Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -995,7 +996,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1011,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>W25 Flip</t>
+          <t>Galaxy S26 Ultra</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1026,8 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>Galaxy S26 FE
+Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -1040,8 +1042,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Galaxy S Series
-Galaxy S26</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1057,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Galaxy S26+</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1071,8 +1072,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Galaxy S26 Ultra
-Galaxy S25</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>Galaxy S25 FE
+Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1103,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1132,8 +1133,8 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE
-Galaxy S24</t>
+          <t>Galaxy S24 FE
+Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1149,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1164,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1178,8 +1179,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE
-Galaxy S23</t>
+          <t>Galaxy S23 FE</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy S26 Ultra</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galaxy S26</t>
+          <t>Galaxy S26 FE</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Galaxy S26+</t>
+          <t>Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Galaxy S26 Ultra</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Galaxy S25</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>Galaxy S25 FE</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S24 FE</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Galaxy S23</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy S23 FE</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,8 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Enterprise Models
+Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1465,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1479,8 +1480,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A54 5G</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,9 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy A57 5G
+Galaxy Tab Active5 Pro
+Galaxy XCover7</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1512,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy XCover7 Pro</t>
         </is>
       </c>
     </row>
@@ -1525,9 +1527,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Galaxy A57 5G
-Galaxy Tab Active5 Pro
-Galaxy XCover7</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy A57 5G</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy Tab Active5 Pro</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Galaxy A57 5G</t>
+          <t>Galaxy XCover7</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5 Pro</t>
+          <t>Galaxy XCover7 Pro</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Galaxy XCover7</t>
+          <t>Galaxy Foldable Series
+Galaxy Z Fold4
+Galaxy Z Flip4</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1644,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy Z Fold4</t>
         </is>
       </c>
     </row>
@@ -1662,9 +1664,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Galaxy Foldable Series
-Galaxy Z Fold3 5G
-Galaxy Z Flip3 5G</t>
+          <t>Galaxy Z Flip4</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,8 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold3 5G</t>
+          <t>Galaxy S Series
+Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1695,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip3 5G</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1709,8 +1710,8 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Galaxy S Series
-Galaxy S22</t>
+          <t>Galaxy S22 Ultra
+Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Galaxy S22+</t>
+          <t>Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1740,8 +1741,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra
-Galaxy S21 FE 5G</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Galaxy S22</t>
+          <t>Galaxy S22 Ultra</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Galaxy S22+</t>
+          <t>Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,8 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra</t>
+          <t>Galaxy A Series
+Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1802,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Galaxy S21 FE 5G</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -1816,8 +1817,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Galaxy A Series
-Galaxy A04</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,8 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A07 5G
+Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1923,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -1937,8 +1938,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G
-Galaxy A14</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,8 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A17 5G
+Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2029,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2043,8 +2044,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G
-Galaxy A23 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,8 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A27 5G
+Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2090,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2104,8 +2105,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G
-Galaxy A33 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,8 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A37 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2151,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2165,8 +2166,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A04s</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A23 5G</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A27 5G</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A37 5G</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,8 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2587,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2601,8 +2602,8 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2618,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2632,8 +2633,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,8 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M07
+Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2664,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2678,8 +2679,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M14</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,8 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M17e 5G
+Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2740,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -2754,8 +2755,8 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G
-Galaxy M34 5G</t>
+          <t>Galaxy M36 5G
+Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2771,8 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M47 5G
+Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2785,8 +2787,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G
-Galaxy M44 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2801,8 +2802,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G
-Galaxy M54 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M47 5G</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,8 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3133,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3147,8 +3148,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,8 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F07
+Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3179,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3194,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3208,8 +3209,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G
-Galaxy F14</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,8 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3240,8 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3256,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3269,8 +3271,8 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F56 5G
+Galaxy F70 Pro 5G</t>
         </is>
       </c>
     </row>
@@ -3285,8 +3287,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3302,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3317,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3332,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3347,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3362,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3377,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3392,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3407,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3422,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3437,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3452,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3467,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3482,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3497,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3512,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy F70 Pro 5G</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3527,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3542,8 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3556,8 +3558,8 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3572,8 +3574,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3589,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3604,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3619,8 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3633,8 +3635,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3650,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3665,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3680,8 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3694,8 +3696,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3711,8 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3725,8 +3727,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3742,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3757,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3772,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3787,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3802,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3817,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3832,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3847,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3862,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3877,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3892,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3907,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3922,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3937,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3952,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3967,8 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -3981,8 +3983,8 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -3997,8 +3999,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4014,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4029,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4044,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab A11+</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4059,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4074,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4089,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4104,9 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Enterprise Models
+Galaxy A53 5G 
+Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4118,9 +4121,8 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A53 5G 
-Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4135,8 +4137,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4152,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy XCover6 Pro</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4167,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4182,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4197,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4212,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4227,8 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Galaxy XCover6 Pro</t>
+          <t>Galaxy Watch Series
+Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4241,8 +4243,8 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch9 40mm</t>
+          <t>Galaxy Watch9 44mm
+Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4257,8 +4259,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 44mm
-Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4274,8 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch8 Classic 46mm
+Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4288,8 +4290,8 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm
-Galaxy Watch Ultra</t>
+          <t>Galaxy Watch Ultra2
+Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4304,8 +4306,9 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra2
-Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch7 44mm
+Galaxy Watch FE
+Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4320,9 +4323,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm
-Galaxy Watch FE
-Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4338,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4353,8 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4367,8 +4369,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4384,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4398,8 +4399,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro
-Galaxy Watch4 40mm</t>
+          <t>Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Watch9 44mm</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 40mm</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 44mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch Ultra2</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra2</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,8 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4670,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4680,13 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4696,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4711,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 40mm</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4726,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 44mm</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4741,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 42mm</t>
+          <t>Galaxy Book4</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4756,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy Watch4 Classic 46mm</t>
+          <t>Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4769,13 +4771,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4785,12 +4786,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4805,8 +4806,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4820,126 +4820,6 @@
         </is>
       </c>
       <c r="C290" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="1" t="n">
-        <v>289</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Pro 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>290</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>291</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Galaxy Book4</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>292</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Ultra</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>293</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="1" t="n">
-        <v>294</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 Pro 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="n">
-        <v>295</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="1" t="n">
-        <v>296</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C290"/>
+  <dimension ref="A1:C292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -1907,8 +1907,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G
-Galaxy A14</t>
+          <t>Galaxy A07s</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1922,8 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A08
+Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2013,8 +2013,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G
-Galaxy A23 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2028,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2043,8 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A18
+Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2074,8 +2074,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G
-Galaxy A33 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2089,8 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A27 5G
+Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2135,8 +2135,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2150,8 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A37 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A04s</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A07s</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A08</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A23 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A18</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A27 5G</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2571,8 +2571,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy A37 5G</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2586,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2602,8 +2601,8 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2617,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2632,8 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2648,8 +2648,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M14</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2663,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2678,8 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M07
+Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2724,8 +2724,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G
-Galaxy M34 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2739,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2755,8 +2754,8 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G
-Galaxy M44 5G</t>
+          <t>Galaxy M17e 5G
+Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2771,8 +2770,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G
-Galaxy M54 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2785,8 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M36 5G
+Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2801,8 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M47 5G
+Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M47 5G</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3117,8 +3117,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3132,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3147,8 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3163,8 +3163,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy F07
-Galaxy F14</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3178,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3193,8 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F07
+Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3224,8 +3224,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3240,8 +3239,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3254,8 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3271,8 +3270,8 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G
-Galaxy F70 Pro 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3286,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3301,8 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F56 5G
+Galaxy F70 Pro 5G</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy F70 Pro 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3542,8 +3542,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy F70 Pro 5G</t>
         </is>
       </c>
     </row>
@@ -3558,8 +3557,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3572,8 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3588,8 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3619,8 +3619,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3634,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3649,8 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3680,8 +3680,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3695,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3711,8 +3710,8 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3726,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3741,8 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3967,8 +3967,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -3983,8 +3982,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3997,8 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4013,8 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A11+</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4104,43 +4104,42 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
+          <t>Galaxy Tab A9+</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Galaxy Tab A9+(2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
           <t>Enterprise Models
 Galaxy A53 5G 
 Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="1" t="n">
-        <v>243</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Galaxy XCover6 Pro</t>
-        </is>
-      </c>
-    </row>
     <row r="246">
       <c r="A246" s="1" t="n">
         <v>244</v>
@@ -4152,7 +4151,8 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Galaxy XCover6 Pro</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4227,8 +4227,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch9 40mm</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4243,8 +4242,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 44mm
-Galaxy Watch8 40mm</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4257,8 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch Series
+Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4274,8 +4273,8 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm
-Galaxy Watch Ultra</t>
+          <t>Galaxy Watch9 44mm
+Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4290,8 +4289,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra2
-Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4306,42 +4304,44 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
+          <t>Galaxy Watch8 Classic 46mm
+Galaxy Watch Ultra</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Galaxy Watch Ultra2
+Galaxy Watch7 40mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
           <t>Galaxy Watch7 44mm
 Galaxy Watch FE
 Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>255</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 44mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="1" t="n">
-        <v>256</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
-        </is>
-      </c>
-    </row>
     <row r="259">
       <c r="A259" s="1" t="n">
         <v>257</v>
@@ -4353,8 +4353,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4368,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4383,8 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 40mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 44mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch9 44mm</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra2</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch Ultra2</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4654,8 +4654,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4669,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4680,13 +4679,13 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4695,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>No Information</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4715,8 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy Book4</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4820,6 +4820,36 @@
         </is>
       </c>
       <c r="C290" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 Pro 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Galaxy Book4 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>

--- a/dataset/samsung_device_updates.xlsx
+++ b/dataset/samsung_device_updates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C292"/>
+  <dimension ref="A1:C291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Galaxy Z Flip8
-W23</t>
+W24</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>W23 Flip</t>
+          <t>W24 Flip</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>W24 Flip</t>
+          <t>W25 Flip</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W26</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>W25 Flip</t>
+          <t>Galaxy Z TriFold</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>Galaxy Z Fold5</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Galaxy Z TriFold</t>
+          <t>Galaxy Z Fold6</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold5</t>
+          <t>Galaxy Z Fold7</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold6</t>
+          <t>Galaxy Z Fold Special Edition</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold7</t>
+          <t>Galaxy Z Fold8</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold Special Edition</t>
+          <t>Galaxy Z Fold8 Ultra</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold8</t>
+          <t>Galaxy Z Flip5</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold8 Ultra</t>
+          <t>Galaxy Z Flip6</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip5</t>
+          <t>Galaxy Z Flip7</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip6</t>
+          <t>Galaxy Z Flip7 FE</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7</t>
+          <t>Galaxy Z Flip8</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip7 FE</t>
+          <t>W24</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip8</t>
+          <t>W24 Flip</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W25</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>W23 Flip</t>
+          <t>W25 Flip</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,8 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>W24 Flip</t>
+          <t>Galaxy S Series
+Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -935,7 +936,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -950,7 +951,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>W25 Flip</t>
+          <t>Galaxy S26 Ultra</t>
         </is>
       </c>
     </row>
@@ -965,7 +966,8 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>Galaxy S26 FE
+Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -980,8 +982,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Galaxy S Series
-Galaxy S26</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -996,7 +997,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Galaxy S26+</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1012,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Galaxy S26 Ultra</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1026,8 +1027,8 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Galaxy S26 FE
-Galaxy S25</t>
+          <t>Galaxy S25 FE
+Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1043,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1058,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1073,8 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>Galaxy S24 FE
+Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1087,8 +1089,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE
-Galaxy S24</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1104,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1119,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S23 FE</t>
         </is>
       </c>
     </row>
@@ -1133,8 +1134,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE
-Galaxy S23</t>
+          <t>Galaxy S26</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy S26+</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Galaxy S26 Ultra</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy S26 FE</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Galaxy S26</t>
+          <t>Galaxy S25</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Galaxy S26+</t>
+          <t>Galaxy S25+</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Galaxy S26 Ultra</t>
+          <t>Galaxy S25 Ultra</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galaxy S26 FE</t>
+          <t>Galaxy S25 Edge</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Galaxy S25</t>
+          <t>Galaxy S25 FE</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Galaxy S25+</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Galaxy S25 Ultra</t>
+          <t>Galaxy S24+</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Galaxy S25 Edge</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Galaxy S25 FE</t>
+          <t>Galaxy S24 FE</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Galaxy S23</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Galaxy S24+</t>
+          <t>Galaxy S23+</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Galaxy S24 Ultra</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Galaxy S24 FE</t>
+          <t>Galaxy S23 FE</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,8 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Galaxy S23</t>
+          <t>Enterprise Models
+Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1405,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Galaxy S23+</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Galaxy S23 Ultra</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1435,9 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Galaxy S23 FE</t>
+          <t>Galaxy A57 5G
+Galaxy Tab Active5 Pro
+Galaxy XCover7</t>
         </is>
       </c>
     </row>
@@ -1449,8 +1452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A54 5G</t>
+          <t>Galaxy XCover7 Pro</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1467,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1482,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy A55 5G</t>
         </is>
       </c>
     </row>
@@ -1495,9 +1497,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Galaxy A57 5G
-Galaxy Tab Active5 Pro
-Galaxy XCover7</t>
+          <t>Galaxy A56 5G</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy A57 5G</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Galaxy A54 5G</t>
+          <t>Galaxy Tab Active5 Pro</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Galaxy A55 5G</t>
+          <t>Galaxy XCover7</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Galaxy A56 5G</t>
+          <t>Galaxy XCover7 Pro</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Galaxy A57 5G</t>
+          <t>Galaxy Foldable Series
+Galaxy Z Fold4
+Galaxy Z Flip4
+W23</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1585,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5 Pro</t>
+          <t>W23 Flip</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1600,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Galaxy XCover7</t>
+          <t>Galaxy Z Fold4</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1615,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Galaxy XCover7 Pro</t>
+          <t>Galaxy Z Flip4</t>
         </is>
       </c>
     </row>
@@ -1632,9 +1635,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Galaxy Foldable Series
-Galaxy Z Fold4
-Galaxy Z Flip4</t>
+          <t>W23</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1650,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Galaxy Z Fold4</t>
+          <t>W23 Flip</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1665,8 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Galaxy Z Flip4</t>
+          <t>Galaxy S Series
+Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1679,8 +1681,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Galaxy S Series
-Galaxy S22</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1696,8 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Galaxy S22+</t>
+          <t>Galaxy S22 Ultra
+Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1710,8 +1712,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra
-Galaxy S21 FE 5G</t>
+          <t>Galaxy S22</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1727,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Galaxy S22</t>
+          <t>Galaxy S22+</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1742,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Galaxy S22+</t>
+          <t>Galaxy S22 Ultra</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1757,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra</t>
+          <t>Galaxy S21 FE 5G</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1772,8 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Galaxy S21 FE 5G</t>
+          <t>Galaxy A Series
+Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -1786,8 +1788,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Galaxy A Series
-Galaxy A04</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1803,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1818,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1833,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1848,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1863,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1878,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1893,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G</t>
+          <t>Galaxy A07s</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1908,8 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Galaxy A07s</t>
+          <t>Galaxy A08
+Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -1922,8 +1924,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Galaxy A08
-Galaxy A14</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1939,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1954,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1969,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1984,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1999,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2014,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2029,8 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A18
+Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2043,8 +2045,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galaxy A18
-Galaxy A24</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2060,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2075,8 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A27 5G
+Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2089,8 +2091,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G
-Galaxy A33 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2106,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2121,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2136,8 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A37 5G
+Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2150,8 +2152,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G
-Galaxy A73 5G</t>
+          <t>Galaxy A04</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2167,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>Galaxy A04e</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2182,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galaxy A04e</t>
+          <t>Galaxy A05</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2197,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Galaxy A05</t>
+          <t>Galaxy A05s</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2212,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galaxy A05s</t>
+          <t>Galaxy A06</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2227,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galaxy A06</t>
+          <t>Galaxy A06 5G</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2242,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galaxy A06 5G</t>
+          <t>Galaxy A07</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2257,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galaxy A07</t>
+          <t>Galaxy A07 5G</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Galaxy A07 5G</t>
+          <t>Galaxy A07s</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2287,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Galaxy A07s</t>
+          <t>Galaxy A08</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2302,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Galaxy A08</t>
+          <t>Galaxy A14</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2317,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Galaxy A14</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2332,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galaxy A14 5G</t>
+          <t>Galaxy A15</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2347,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galaxy A15</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2362,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Galaxy A15 5G</t>
+          <t>Galaxy A16</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2377,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Galaxy A16</t>
+          <t>Galaxy A16 5G</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2392,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Galaxy A16 5G</t>
+          <t>Galaxy A17</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2407,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Galaxy A17</t>
+          <t>Galaxy A17 5G</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2422,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Galaxy A17 5G</t>
+          <t>Galaxy A18</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2437,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galaxy A18</t>
+          <t>Galaxy A24</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2452,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Galaxy A24</t>
+          <t>Galaxy A25 5G</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2467,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Galaxy A25 5G</t>
+          <t>Galaxy A26 5G</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2482,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Galaxy A26 5G</t>
+          <t>Galaxy A27 5G</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2497,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Galaxy A27 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2512,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A34 5G</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2527,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Galaxy A34 5G</t>
+          <t>Galaxy A35 5G</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2542,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Galaxy A35 5G</t>
+          <t>Galaxy A36 5G</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2557,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Galaxy A36 5G</t>
+          <t>Galaxy A37 5G</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2572,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Galaxy A37 5G</t>
+          <t>Galaxy A73 5G</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2587,8 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Galaxy A73 5G</t>
+          <t>Galaxy C Series
+Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2601,8 +2603,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Galaxy C Series
-Galaxy C55 5G</t>
+          <t>Galaxy C55 5G</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2618,8 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galaxy C55 5G</t>
+          <t>Galaxy M Series
+Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2632,8 +2634,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy M Series
-Galaxy M04</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2649,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2664,8 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M07
+Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2678,8 +2680,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Galaxy M07
-Galaxy M14</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2695,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2710,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2725,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2740,8 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M17e 5G
+Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -2754,8 +2756,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G
-Galaxy M34 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2771,8 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M36 5G
+Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -2785,8 +2787,8 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G
-Galaxy M44 5G</t>
+          <t>Galaxy M47 5G
+Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -2801,8 +2803,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G
-Galaxy M54 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2818,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2833,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2848,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy M04</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2863,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Galaxy M04</t>
+          <t>Galaxy M05</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2878,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Galaxy M05</t>
+          <t>Galaxy M06 5G</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2893,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Galaxy M06 5G</t>
+          <t>Galaxy M07</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2908,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Galaxy M07</t>
+          <t>Galaxy M14</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2923,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Galaxy M14</t>
+          <t>Galaxy M14 5G</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2938,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Galaxy M14 5G</t>
+          <t>Galaxy M15 5G</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2953,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Galaxy M15 5G</t>
+          <t>Galaxy M16 5G</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2968,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Galaxy M16 5G</t>
+          <t>Galaxy M17 5G</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2983,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Galaxy M17 5G</t>
+          <t>Galaxy M17e 5G</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2998,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Galaxy M17e 5G</t>
+          <t>Galaxy M34 5G</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3013,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Galaxy M34 5G</t>
+          <t>Galaxy M35 5G</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3028,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Galaxy M35 5G</t>
+          <t>Galaxy M36 5G</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3043,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Galaxy M36 5G</t>
+          <t>Galaxy M44 5G</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3058,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Galaxy M44 5G</t>
+          <t>Galaxy M47 5G</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3073,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Galaxy M47 5G</t>
+          <t>Galaxy M54 5G</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3088,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Galaxy M54 5G</t>
+          <t>Galaxy M55 5G</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3103,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Galaxy M55 5G</t>
+          <t>Galaxy M55s 5G</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3118,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Galaxy M55s 5G</t>
+          <t>Galaxy M56 5G</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3133,8 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Galaxy M56 5G</t>
+          <t>Galaxy F Series
+Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3147,8 +3149,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Galaxy F Series
-Galaxy F04</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3164,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3179,8 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F07
+Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3193,8 +3195,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Galaxy F07
-Galaxy F14</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3210,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3225,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3240,8 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F17 5G
+Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3254,8 +3256,8 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G
-Galaxy F34 5G</t>
+          <t>Galaxy F36 5G
+Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3270,8 +3272,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G
-Galaxy F54 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3287,8 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F56 5G
+Galaxy F70 Pro 5G</t>
         </is>
       </c>
     </row>
@@ -3301,8 +3303,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G
-Galaxy F70 Pro 5G</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3318,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy F04</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3333,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Galaxy F04</t>
+          <t>Galaxy F05</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3348,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Galaxy F05</t>
+          <t>Galaxy F06 5G</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3363,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Galaxy F06 5G</t>
+          <t>Galaxy F07</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3378,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Galaxy F07</t>
+          <t>Galaxy F14</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3393,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Galaxy F14</t>
+          <t>Galaxy F14 5G</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3408,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Galaxy F14 5G</t>
+          <t>Galaxy F15 5G</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Galaxy F15 5G</t>
+          <t>Galaxy F16 5G</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3438,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Galaxy F16 5G</t>
+          <t>Galaxy F17 5G</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3453,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Galaxy F17 5G</t>
+          <t>Galaxy F34 5G</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3468,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Galaxy F34 5G</t>
+          <t>Galaxy F36 5G</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3483,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Galaxy F36 5G</t>
+          <t>Galaxy F54 5G</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3498,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Galaxy F54 5G</t>
+          <t>Galaxy F55 5G</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3513,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Galaxy F55 5G</t>
+          <t>Galaxy F56 5G</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3528,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Galaxy F56 5G</t>
+          <t>Galaxy F70 Pro 5G</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3543,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Galaxy F70 Pro 5G</t>
+          <t>Galaxy F70e 5G</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3558,8 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Galaxy F70e 5G</t>
+          <t>Galaxy Tab S Series
+Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3572,8 +3574,8 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Galaxy Tab S Series
-Galaxy Tab S11</t>
+          <t>Galaxy Tab S11 Ultra
+Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3588,8 +3590,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra
-Galaxy Tab S10+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3605,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3620,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3635,8 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Lite
+Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3649,8 +3651,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite
-Galaxy Tab S9</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3666,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3681,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3696,8 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9 FE+
+Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3710,8 +3712,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+
-Galaxy Tab S8</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3727,8 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S8 Ultra
+Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3741,8 +3743,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra
-Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab S11</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3758,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11</t>
+          <t>Galaxy Tab S11 Ultra</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3773,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Galaxy Tab S11 Ultra</t>
+          <t>Galaxy Tab S10+</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3788,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10+</t>
+          <t>Galaxy Tab S10 Ultra</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3803,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Ultra</t>
+          <t>Galaxy Tab S10 FE</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3818,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE</t>
+          <t>Galaxy Tab S10 FE+</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3833,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 FE+</t>
+          <t>Galaxy Tab S10 Lite</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3848,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Galaxy Tab S10 Lite</t>
+          <t>Galaxy Tab S9</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3863,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9</t>
+          <t>Galaxy Tab S9+</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3878,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9+</t>
+          <t>Galaxy Tab S9 Ultra</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3893,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 Ultra</t>
+          <t>Galaxy Tab S9 FE</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3908,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE</t>
+          <t>Galaxy Tab S9 FE+</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3923,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Galaxy Tab S9 FE+</t>
+          <t>Galaxy Tab S8</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3938,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8</t>
+          <t>Galaxy Tab S8+</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3953,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8+</t>
+          <t>Galaxy Tab S8 Ultra</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3968,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Galaxy Tab S8 Ultra</t>
+          <t>Galaxy Tab S6 Lite (2024)</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3983,8 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Galaxy Tab S6 Lite (2024)</t>
+          <t>Galaxy Tab A Series
+Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -3997,8 +3999,8 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Galaxy Tab A Series
-Galaxy Tab A11</t>
+          <t>Galaxy Tab A11+
+Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4013,8 +4015,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+
-Galaxy Tab A9</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4030,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4045,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Galaxy Tab A11</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4060,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11</t>
+          <t>Galaxy Tab A11+</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4075,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Galaxy Tab A11+</t>
+          <t>Galaxy Tab A9</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4090,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9</t>
+          <t>Galaxy Tab A9+</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4105,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+</t>
+          <t>Galaxy Tab A9+(2025)</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4120,9 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Galaxy Tab A9+(2025)</t>
+          <t>Enterprise Models
+Galaxy A53 5G 
+Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4134,9 +4137,8 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Enterprise Models
-Galaxy A53 5G 
-Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab Active5
+Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4151,8 +4153,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5
-Galaxy XCover5</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4168,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Galaxy XCover6 Pro</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4183,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy Tab Active4 Pro</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4198,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active4 Pro</t>
+          <t>Galaxy Tab Active5</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4213,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Galaxy Tab Active5</t>
+          <t>Galaxy XCover5</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4228,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Galaxy XCover5</t>
+          <t>Galaxy XCover6 Pro</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4243,8 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Galaxy XCover6 Pro</t>
+          <t>Galaxy Watch Series
+Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4257,8 +4259,8 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Galaxy Watch Series
-Galaxy Watch9 40mm</t>
+          <t>Galaxy Watch9 44mm
+Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4273,8 +4275,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 44mm
-Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4290,8 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch8 Classic 46mm
+Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4304,8 +4306,8 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm
-Galaxy Watch Ultra</t>
+          <t>Galaxy Watch Ultra2
+Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4320,8 +4322,9 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra2
-Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch7 44mm
+Galaxy Watch FE
+Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4336,9 +4339,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm
-Galaxy Watch FE
-Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4354,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4369,8 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch6 Classic 47mm
+Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4383,8 +4385,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm
-Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4400,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4415,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy Watch9 40mm</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4430,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 40mm</t>
+          <t>Galaxy Watch9 44mm</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4445,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Galaxy Watch9 44mm</t>
+          <t>Galaxy Watch8 40mm</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4460,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 40mm</t>
+          <t>Galaxy Watch8 44mm</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4475,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 44mm</t>
+          <t>Galaxy Watch8 Classic 46mm</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4490,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Galaxy Watch8 Classic 46mm</t>
+          <t>Galaxy Watch Ultra</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4505,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra</t>
+          <t>Galaxy Watch Ultra2</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4520,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Galaxy Watch Ultra2</t>
+          <t>Galaxy Watch7 40mm</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4535,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 40mm</t>
+          <t>Galaxy Watch7 44mm</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4550,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galaxy Watch7 44mm</t>
+          <t>Galaxy Watch FE</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4565,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galaxy Watch FE</t>
+          <t>Galaxy Watch6 40mm</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4580,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 40mm</t>
+          <t>Galaxy Watch6 44mm</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4595,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 44mm</t>
+          <t>Galaxy Watch6 Classic 43mm</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4610,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 43mm</t>
+          <t>Galaxy Watch6 Classic 47mm</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4625,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Galaxy Watch6 Classic 47mm</t>
+          <t>Galaxy Watch5 40mm</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4640,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 40mm</t>
+          <t>Galaxy Watch5 44mm</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4655,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 44mm</t>
+          <t>Galaxy Watch5 Pro</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4670,8 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Galaxy Watch5 Pro</t>
+          <t>Galaxy XR Series
+Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4684,8 +4686,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Galaxy XR Series
-Galaxy XR</t>
+          <t>Galaxy XR</t>
         </is>
       </c>
     </row>
@@ -4695,12 +4696,13 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>No Information</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Galaxy XR</t>
+          <t>Galaxy Book Series
+Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4715,8 +4717,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Galaxy Book Series
-Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4732,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4747,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4762,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Galaxy Book4 360</t>
+          <t>Galaxy Book4</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4777,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Galaxy Book4</t>
+          <t>Galaxy Book4 Ultra</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4792,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Ultra</t>
+          <t>Galaxy Book4 Pro</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4807,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro</t>
+          <t>Galaxy Book4 Pro 360</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4822,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Galaxy Book4 Pro 360</t>
+          <t>Galaxy Book4 360</t>
         </is>
       </c>
     </row>
@@ -4835,21 +4836,6 @@
         </is>
       </c>
       <c r="C291" t="inlineStr">
-        <is>
-          <t>Galaxy Book4 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>290</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
         <is>
           <t>Galaxy Book4</t>
         </is>
